--- a/r5-aist-trustworthyai-poc-pipeline/CodeSystem-gdpr-art6-codesystem.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/CodeSystem-gdpr-art6-codesystem.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>GDPR Art 6 Legal Basis</t>
+    <t>GDPR Article 6 Legal Basis CodeSystem</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Codes representing legal bases for processing personal data according to GDPR Article 6.</t>
+    <t>Code system defining GDPR Article 6 legal bases relevant for documenting legal-basis metadata in AI-supported processing contexts.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>6</t>
   </si>
   <si>
     <t>Level</t>
@@ -147,10 +147,28 @@
     <t>Contract (Art. 6(1)(b))</t>
   </si>
   <si>
+    <t>gdpr-art-6-1-c</t>
+  </si>
+  <si>
+    <t>Legal Obligation (Art. 6(1)(c))</t>
+  </si>
+  <si>
     <t>gdpr-art-6-1-d</t>
   </si>
   <si>
     <t>Vital Interests (Art. 6(1)(d))</t>
+  </si>
+  <si>
+    <t>gdpr-art-6-1-e</t>
+  </si>
+  <si>
+    <t>Public Interest or Official Authority (Art. 6(1)(e))</t>
+  </si>
+  <si>
+    <t>gdpr-art-6-1-f</t>
+  </si>
+  <si>
+    <t>Legitimate Interests (Art. 6(1)(f))</t>
   </si>
 </sst>
 </file>
@@ -452,7 +470,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -505,6 +523,42 @@
       </c>
       <c r="D4" s="2"/>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
